--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486522_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486522_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.133</v>
+        <v>12.7508</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3376</v>
+        <v>7.202</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7954</v>
+        <v>5.5488</v>
       </c>
       <c r="G2" t="n">
         <v>5.8568</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2783</v>
+        <v>2.8961</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8348</v>
+        <v>1.6992</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4435</v>
+        <v>1.1969</v>
       </c>
       <c r="V2" t="n">
         <v>3.7804</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1532</v>
+        <v>4.6825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9651</v>
+        <v>1.6176</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1881</v>
+        <v>3.0649</v>
       </c>
       <c r="G3" t="n">
         <v>0.9261</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5088</v>
+        <v>2.0381</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3257</v>
+        <v>0.9782</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1832</v>
+        <v>1.0599</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1093</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7114</v>
+        <v>2.522</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6808</v>
+        <v>2.1319</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0306</v>
+        <v>0.3901</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9264</v>
+        <v>1.8736</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7822</v>
+        <v>2.0831</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8558</v>
+        <v>-0.2096</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8697</v>
+        <v>2.1463</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5964</v>
+        <v>2.3359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7267</v>
+        <v>-0.1896</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0567</v>
+        <v>-0.2727</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1858</v>
+        <v>-0.2528</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>-0.0199</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>5.7699</v>
+        <v>1.4309</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1399</v>
+        <v>1.0731</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6301</v>
+        <v>0.3578</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1941</v>
+        <v>2.2112</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0814</v>
+        <v>-0.8351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1127</v>
+        <v>3.0463</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8736</v>
+        <v>0.3131</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0831</v>
+        <v>0.2007</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2096</v>
+        <v>0.1124</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1463</v>
+        <v>-0.0461</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3359</v>
+        <v>0.3531</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1896</v>
+        <v>-0.3992</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2727</v>
+        <v>0.3592</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2528</v>
+        <v>-0.1523</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0199</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.103</v>
+        <v>0.8105</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0227</v>
+        <v>0.1034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0804</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7227</v>
+        <v>2.0356</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0153</v>
+        <v>-0.8558</v>
       </c>
       <c r="F6" t="n">
-        <v>2.738</v>
+        <v>2.8913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3131</v>
+        <v>0.3365</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2007</v>
+        <v>0.0911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1124</v>
+        <v>0.2454</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0461</v>
+        <v>-0.3542</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3531</v>
+        <v>-0.0881</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3992</v>
+        <v>-0.2661</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3592</v>
+        <v>0.6907</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1523</v>
+        <v>0.1792</v>
       </c>
       <c r="O6" t="n">
         <v>0.5116000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3221</v>
+        <v>1.1792</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0769</v>
+        <v>0.5011</v>
       </c>
       <c r="U6" t="n">
-        <v>0.399</v>
+        <v>0.678</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5197000000000001</v>
+        <v>1.7105</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5774</v>
+        <v>-0.5715</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0971</v>
+        <v>2.282</v>
       </c>
       <c r="G7" t="n">
         <v>0.8054</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2432</v>
+        <v>0.9475</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5102</v>
+        <v>0.6952</v>
       </c>
       <c r="V7" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1954</v>
+        <v>0.8427</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1103</v>
+        <v>-0.4174</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3057</v>
+        <v>1.2601</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3365</v>
+        <v>-0.9264</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0911</v>
+        <v>-1.7822</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2454</v>
+        <v>0.8558</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3542</v>
+        <v>-0.8697</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0881</v>
+        <v>-1.5964</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2661</v>
+        <v>0.7267</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6907</v>
+        <v>-0.0567</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1792</v>
+        <v>-0.1858</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.1291</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6611</v>
+        <v>2.9012</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>2.0417</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0924</v>
+        <v>0.8595</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2599</v>
+        <v>0.3904</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2599</v>
+        <v>0.5857</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1557</v>
+        <v>0.3334</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.137</v>
+        <v>-0.5985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2927</v>
+        <v>0.9319</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2311</v>
+        <v>0.4422</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.067</v>
+        <v>-1.2408</v>
       </c>
       <c r="I9" t="n">
-        <v>0.298</v>
+        <v>1.683</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.596</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-1.1069</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7029</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2311</v>
+        <v>-0.1539</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.067</v>
+        <v>-0.1339</v>
       </c>
       <c r="O9" t="n">
-        <v>0.298</v>
+        <v>-0.0199</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.3263</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>-0.1069</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0616</v>
+        <v>0.4332</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.103</v>
+        <v>0.3167</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8905</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935</v>
+        <v>0.3852</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4422</v>
+        <v>0.2311</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2408</v>
+        <v>-0.067</v>
       </c>
       <c r="I10" t="n">
-        <v>1.683</v>
+        <v>0.298</v>
       </c>
       <c r="J10" t="n">
-        <v>0.596</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1069</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7029</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1539</v>
+        <v>0.2311</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1339</v>
+        <v>-0.067</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0199</v>
+        <v>0.298</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0959</v>
+        <v>0.0856</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4949</v>
+        <v>0.1541</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5411</v>
+        <v>-0.7075</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6669</v>
+        <v>-1.8091</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1258</v>
+        <v>1.1016</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1885</v>
+        <v>-3.9037</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1343</v>
+        <v>-1.8614</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0542</v>
+        <v>-2.0423</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1892</v>
+        <v>-3.3665</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3039</v>
+        <v>-1.3441</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1147</v>
+        <v>-2.0224</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9994</v>
+        <v>-0.5372</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8304</v>
+        <v>-0.5173</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1689</v>
+        <v>-0.0199</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2776</v>
+        <v>2.0864</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4146</v>
+        <v>1.5574</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8631</v>
+        <v>0.529</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9565</v>
+        <v>-1.1662</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0889</v>
+        <v>-1.0454</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1324</v>
+        <v>-0.1208</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9037</v>
+        <v>-1.1885</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8614</v>
+        <v>-1.1343</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0423</v>
+        <v>-0.0542</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3665</v>
+        <v>-0.1892</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3441</v>
+        <v>-0.3039</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0224</v>
+        <v>0.1147</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5372</v>
+        <v>-0.9994</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5173</v>
+        <v>-0.8304</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0199</v>
+        <v>-0.1689</v>
       </c>
       <c r="P12" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8375</v>
+        <v>0.6525</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2776</v>
+        <v>0.0361</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5599</v>
+        <v>0.6165</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1952</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4813</v>
+        <v>-3.9097</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4652</v>
+        <v>-4.9244</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9838</v>
+        <v>1.0147</v>
       </c>
       <c r="G13" t="n">
         <v>0.4013</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7295</v>
+        <v>1.3011</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1286</v>
+        <v>0.6694</v>
       </c>
       <c r="U13" t="n">
-        <v>0.601</v>
+        <v>0.6318</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1745</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.9093</v>
+        <v>21.622</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.886600000000001</v>
+        <v>-0.1742000000000017</v>
       </c>
       <c r="F14" t="n">
-        <v>21.7958</v>
+        <v>21.79610000000001</v>
       </c>
       <c r="G14" t="n">
         <v>5.1675</v>
       </c>
       <c r="H14" t="n">
-        <v>1.565499999999999</v>
+        <v>1.565500000000001</v>
       </c>
       <c r="I14" t="n">
         <v>3.6018</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4119</v>
+        <v>3.411899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>4.503499999999999</v>
+        <v>4.5035</v>
       </c>
       <c r="L14" t="n">
         <v>-1.0915</v>
@@ -1534,7 +1534,7 @@
         <v>-2.938</v>
       </c>
       <c r="O14" t="n">
-        <v>4.693600000000001</v>
+        <v>4.6936</v>
       </c>
       <c r="P14" t="n">
         <v>-3.262700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>16.3129</v>
       </c>
       <c r="S14" t="n">
-        <v>14.943</v>
+        <v>16.6554</v>
       </c>
       <c r="T14" t="n">
-        <v>7.023999999999999</v>
+        <v>8.736599999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>7.919300000000001</v>
+        <v>7.9191</v>
       </c>
       <c r="V14" t="n">
         <v>3.061500000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5654</v>
+        <v>4.9334</v>
       </c>
       <c r="E15" t="n">
-        <v>2.606</v>
+        <v>2.1589</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9594</v>
+        <v>2.7745</v>
       </c>
       <c r="G15" t="n">
         <v>4.6867</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-1.3633</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2704</v>
+        <v>-0.7174</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.461</v>
+        <v>-0.6459</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5649999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9954</v>
+        <v>1.2809</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4244</v>
+        <v>-1.038</v>
       </c>
       <c r="F16" t="n">
-        <v>0.571</v>
+        <v>2.3189</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4191</v>
+        <v>3.2678</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7832</v>
+        <v>2.424</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3642</v>
+        <v>0.8439</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8822</v>
+        <v>2.8839</v>
       </c>
       <c r="K16" t="n">
-        <v>3.334</v>
+        <v>2.5763</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4519</v>
+        <v>0.3076</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5369</v>
+        <v>0.3839</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5508</v>
+        <v>-0.1523</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0877</v>
+        <v>0.5362</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>3.2626</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4438</v>
+        <v>-2.4872</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>-1.1596</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.968</v>
+        <v>-1.3276</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2806</v>
+        <v>-0.3698</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5809</v>
+        <v>0.6178</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3733</v>
+        <v>0.2008</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9542</v>
+        <v>0.4169</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2678</v>
+        <v>2.4191</v>
       </c>
       <c r="H17" t="n">
-        <v>2.424</v>
+        <v>2.7832</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8439</v>
+        <v>-0.3642</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8839</v>
+        <v>1.8822</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5763</v>
+        <v>3.334</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3076</v>
+        <v>-1.4519</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3839</v>
+        <v>0.5369</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1523</v>
+        <v>-0.5508</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5362</v>
+        <v>1.0877</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2626</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.1873</v>
+        <v>-1.8215</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4949</v>
+        <v>-0.6994</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6924</v>
+        <v>-1.1221</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3698</v>
+        <v>2.2806</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1441</v>
+        <v>-1.1415</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9345</v>
+        <v>-3.711</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7904</v>
+        <v>2.5695</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5117</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3067</v>
+        <v>-0.304</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3014</v>
+        <v>-1.0779</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9947</v>
+        <v>0.7739</v>
       </c>
       <c r="V18" t="n">
         <v>1.6743</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4513</v>
+        <v>-2.5245</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9445</v>
+        <v>-1.8327</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5068</v>
+        <v>-0.6918</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1723</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9114</v>
+        <v>-1.9846</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1644</v>
+        <v>-1.0527</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.747</v>
+        <v>-0.9319</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8902</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5865</v>
+        <v>-2.6752</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8043</v>
+        <v>0.469</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3908</v>
+        <v>-3.1442</v>
       </c>
       <c r="G20" t="n">
         <v>0.4818</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7006</v>
+        <v>-1.7893</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0036</v>
+        <v>-0.3317</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7043</v>
+        <v>-1.4577</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4552</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.506</v>
+        <v>-3.5189</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1339</v>
+        <v>-2.3574</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3722</v>
+        <v>-1.1615</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4782</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5069</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1454</v>
+        <v>-0.3689</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3615</v>
+        <v>-0.1508</v>
       </c>
       <c r="V21" t="n">
         <v>1.479</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.6573</v>
+        <v>-6.8841</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6813</v>
+        <v>-5.4578</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.976</v>
+        <v>-1.4263</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7219</v>
@@ -2170,13 +2170,13 @@
         <v>2.6101</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7179</v>
+        <v>-1.9446</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7809</v>
+        <v>-1.5574</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.3873</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.7058</v>
+        <v>-9.2523</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.563</v>
+        <v>-10.2278</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8572</v>
+        <v>0.9754</v>
       </c>
       <c r="G23" t="n">
         <v>-8.1387</v>
@@ -2248,13 +2248,13 @@
         <v>3.0451</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4372</v>
+        <v>-1.9837</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2894</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1478</v>
+        <v>-1.0296</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.9093</v>
+        <v>-19.1644</v>
       </c>
       <c r="E24" t="n">
-        <v>-21.7958</v>
+        <v>-21.796</v>
       </c>
       <c r="F24" t="n">
-        <v>1.886399999999999</v>
+        <v>2.631400000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1674</v>
+        <v>-5.167400000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-1.565700000000001</v>
@@ -2326,16 +2326,16 @@
         <v>19.5757</v>
       </c>
       <c r="S24" t="n">
-        <v>-14.9432</v>
+        <v>-14.1979</v>
       </c>
       <c r="T24" t="n">
         <v>-7.9191</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.0243</v>
+        <v>-6.279</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.061599999999999</v>
+        <v>-3.0616</v>
       </c>
       <c r="W24" t="n">
         <v>4.1915</v>
